--- a/EPIC-0001.xlsx
+++ b/EPIC-0001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF9E44F-CAAF-49EC-B567-9C6CC7383DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF82DD6A-4107-4088-918A-4491213F18F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
